--- a/AAII_Financials/Yearly/COVTY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/COVTY_YR_FIN.xlsx
@@ -2171,10 +2171,10 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>1723600</v>
+        <v>1729500</v>
       </c>
       <c r="E58" s="3">
-        <v>726800</v>
+        <v>737100</v>
       </c>
       <c r="F58" s="3">
         <v>720700</v>
@@ -2204,10 +2204,10 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>435600</v>
+        <v>429700</v>
       </c>
       <c r="E59" s="3">
-        <v>636700</v>
+        <v>626400</v>
       </c>
       <c r="F59" s="3">
         <v>674300</v>
